--- a/christmas_forms/006_secret_santa_form--christmas_forms.xlsx
+++ b/christmas_forms/006_secret_santa_form--christmas_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -761,8 +761,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -824,12 +824,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_50096,_'label':_'form_1'}</t>
+          <t>form_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 50096, 'label': 'Form 1'}</t>
+          <t>Form 1</t>
         </is>
       </c>
     </row>
@@ -841,12 +841,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_50167,_'label':_'form_2'}</t>
+          <t>form_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 50167, 'label': 'Form 2'}</t>
+          <t>Form 2</t>
         </is>
       </c>
     </row>
@@ -858,12 +858,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_'chatjimmy',_'label':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 'chatjimmy', 'label': 'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_'chatfrank',_'label':_'chatfrank'}</t>
+          <t>chatfrank</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 'chatfrank', 'label': 'chatfrank'}</t>
+          <t>chatfrank</t>
         </is>
       </c>
     </row>
@@ -892,12 +892,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_'chatjess',_'label':_'chatjess'}</t>
+          <t>chatjess</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 'chatjess', 'label': 'chatjess'}</t>
+          <t>chatjess</t>
         </is>
       </c>
     </row>
